--- a/Employee_Reports_wi52/Michael Jorge Toscano Masaoy Q0616.xlsx
+++ b/Employee_Reports_wi52/Michael Jorge Toscano Masaoy Q0616.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1379,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1428,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7991</v>
+        <v>7983</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
